--- a/input/timetable/Физическая культура для лиц с откл. в сост. здор.xlsx
+++ b/input/timetable/Физическая культура для лиц с откл. в сост. здор.xlsx
@@ -272,9 +272,6 @@
     <t>Психология физической культуры (лек), К202//</t>
   </si>
   <si>
-    <t>Русский язык и культура речи (пр), К426</t>
-  </si>
-  <si>
     <t>ФТД: Цифровая грамотность (пр), К706</t>
   </si>
   <si>
@@ -329,9 +326,6 @@
     <t xml:space="preserve">Биохимия мышечной деятельности (лек), А539// </t>
   </si>
   <si>
-    <t>Биохимия мышечной деятельности (пр),  А439//  Физиология человека (пр), А433</t>
-  </si>
-  <si>
     <t>Формирование культуры здорового образа жизни (лек). К210//</t>
   </si>
   <si>
@@ -339,6 +333,12 @@
   </si>
   <si>
     <t>Физиология человека (лек), А204</t>
+  </si>
+  <si>
+    <t>Биохимия мышечной деятельности (пр),  А439//  Физиология человека (пр), А431</t>
+  </si>
+  <si>
+    <t>Русский язык и культура речи (пр), К709</t>
   </si>
 </sst>
 </file>
@@ -2194,7 +2194,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="74" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" s="75"/>
       <c r="E11" s="75"/>
@@ -2206,7 +2206,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" s="75"/>
       <c r="E12" s="75"/>
@@ -2254,7 +2254,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65"/>
@@ -2300,7 +2300,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="90" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D20" s="91"/>
       <c r="E20" s="91"/>
@@ -2312,7 +2312,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" s="94"/>
       <c r="E21" s="94"/>
@@ -2360,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="84" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D25" s="85"/>
       <c r="E25" s="85"/>
@@ -2372,7 +2372,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="74" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D26" s="75"/>
       <c r="E26" s="75"/>
@@ -2428,7 +2428,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D31" s="138"/>
       <c r="E31" s="139" t="s">
@@ -2498,7 +2498,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="120" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D37" s="121"/>
       <c r="E37" s="121"/>
@@ -2805,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="143" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" s="144"/>
       <c r="E14" s="144"/>
@@ -2851,7 +2851,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="71" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D18" s="72"/>
       <c r="E18" s="72"/>
@@ -2863,7 +2863,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="93" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D19" s="94"/>
       <c r="E19" s="94"/>
@@ -2945,7 +2945,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="173" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D26" s="174"/>
       <c r="E26" s="175" t="s">
@@ -3359,7 +3359,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="96" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D18" s="97"/>
       <c r="E18" s="97"/>
@@ -3371,7 +3371,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="146" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="193"/>
       <c r="E19" s="193"/>
@@ -3515,7 +3515,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D31" s="94"/>
       <c r="E31" s="94"/>
@@ -3527,7 +3527,7 @@
         <v>3</v>
       </c>
       <c r="C32" s="77" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" s="78"/>
       <c r="E32" s="78"/>
@@ -3758,7 +3758,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="204" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11" s="205"/>
       <c r="E11" s="205"/>
@@ -3770,7 +3770,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="207" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" s="208"/>
       <c r="E12" s="208"/>
@@ -3900,7 +3900,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="222" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="223"/>
       <c r="E23" s="223"/>
@@ -3912,7 +3912,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="207" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D24" s="208"/>
       <c r="E24" s="208"/>
@@ -3948,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="108" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D27" s="109"/>
       <c r="E27" s="109"/>
@@ -3960,7 +3960,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="213" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D28" s="214"/>
       <c r="E28" s="214"/>

--- a/input/timetable/Физическая культура для лиц с откл. в сост. здор.xlsx
+++ b/input/timetable/Физическая культура для лиц с откл. в сост. здор.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28755" windowHeight="13980" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28755" windowHeight="13980"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="140">
   <si>
     <t>пара</t>
   </si>
@@ -77,6 +77,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -128,18 +131,39 @@
     <t>Лыжный спорт с методикой преподавания, л/б</t>
   </si>
   <si>
+    <t>Мальков М.Н,, Жулепов В.И.</t>
+  </si>
+  <si>
+    <t>Аустер Л.В., Родионова М.А.</t>
+  </si>
+  <si>
     <t>Гимнастика с методикой преподавания, Зал гимн.</t>
   </si>
   <si>
+    <t>Булгакова О.В., Савиных Л.Е.</t>
+  </si>
+  <si>
     <t>Спортивно-педагогические дисциплины, Зал гимн</t>
   </si>
   <si>
+    <t>Савиных Л.Е., Булгакова О.В.</t>
+  </si>
+  <si>
     <t>Плавание с методикой преподавания/Спортивно-педагогические дисциплины,  Бассейн (с 13.15)</t>
   </si>
   <si>
+    <t>Шнейдер В.Ю.</t>
+  </si>
+  <si>
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Мальков М.Н., Жулепов В.И.</t>
+  </si>
+  <si>
+    <t>Жулепов В.И.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
@@ -149,9 +173,21 @@
     <t>Биомеханика двигательной деятельности (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Григорьев В.А.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (пр), К210</t>
   </si>
   <si>
+    <t>Воронюк Т.В.</t>
+  </si>
+  <si>
+    <t>Синюкова Т.А.</t>
+  </si>
+  <si>
+    <t>Юденко И.Э.</t>
+  </si>
+  <si>
     <t>Комплексный контроль в адаптивной физической культуре (лек), К210</t>
   </si>
   <si>
@@ -161,18 +197,36 @@
     <t>День самостоятельной работы</t>
   </si>
   <si>
+    <t>Ветошников А.Ю.</t>
+  </si>
+  <si>
+    <t>Давыдова А.М.</t>
+  </si>
+  <si>
     <t>Технологии спортивной тренировки в избранном виде спорта (пр), К210а</t>
   </si>
   <si>
+    <t>Солодилов Р.О.</t>
+  </si>
+  <si>
     <t>206-31</t>
   </si>
   <si>
+    <t>Белоус П.В.</t>
+  </si>
+  <si>
     <t>Плавание с методикой преподавания, бассейн (с 13.15)</t>
   </si>
   <si>
     <t>Спортивно-педагогические дисциплины, ЦАС//</t>
   </si>
   <si>
+    <t>Вагидова А.Х, Снигирев А.С.</t>
+  </si>
+  <si>
+    <t>Замятина М.С.</t>
+  </si>
+  <si>
     <t>Материально-техническое обеспечение адаптивной физической культуры (лек)/(пр), К210а</t>
   </si>
   <si>
@@ -185,6 +239,15 @@
     <t>История России (лекция 32 ч)</t>
   </si>
   <si>
+    <t>Афян К.А.; Бастинович Е.В.</t>
+  </si>
+  <si>
+    <t>Снигирев А.С., Вагидова А.Х.</t>
+  </si>
+  <si>
+    <t>Говорухина А.А.</t>
+  </si>
+  <si>
     <t>Легкая атлетика с методикой преподавания, ЦАС</t>
   </si>
   <si>
@@ -206,9 +269,15 @@
     <t>Иностранный язык, п/г 2, А502</t>
   </si>
   <si>
+    <t>Кочиева Д.И.</t>
+  </si>
+  <si>
     <t>Адаптивный спорт, сп/з//  Физическая реабилитация (пр), сп/з</t>
   </si>
   <si>
+    <t>Жулепов В.И./Юденко И.Э.</t>
+  </si>
+  <si>
     <t>Частные методики адаптивной физической культуры (лек), К210а//</t>
   </si>
   <si>
@@ -230,6 +299,9 @@
     <t xml:space="preserve">                       РАСПИСАНИЕ УЧЕБНЫХ ЗАНЯТИЙ </t>
   </si>
   <si>
+    <t>Кузнецов А.С.</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Проректор по УМР</t>
   </si>
   <si>
@@ -254,12 +326,42 @@
     <t>02.02.2026-08.04.2026</t>
   </si>
   <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
+    <t>Вариясова Е.В.</t>
+  </si>
+  <si>
     <t>//Спортивно-педагогические дисциплины, ЦАС</t>
   </si>
   <si>
+    <t>Литовченко О.Г.</t>
+  </si>
+  <si>
+    <t>Говорухина А.А./Барсегян С.Т.</t>
+  </si>
+  <si>
+    <t>Лосев А.В.</t>
+  </si>
+  <si>
+    <t>Ветрова Д.Н.</t>
+  </si>
+  <si>
+    <t>Гпврилова Н.В.</t>
+  </si>
+  <si>
+    <t>Гаврилова Н.В.</t>
+  </si>
+  <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
     <t>Учебная практика, педагогическая практика, К210//</t>
   </si>
   <si>
+    <t>Мальков М.Н.</t>
+  </si>
+  <si>
     <t>Частные методики адаптивной физической культуры (пр), сп/з</t>
   </si>
   <si>
@@ -276,6 +378,9 @@
   </si>
   <si>
     <t>Иностранный язык, п/г 1, А501</t>
+  </si>
+  <si>
+    <t>Замятина М.С./Калинина Е.А.</t>
   </si>
   <si>
     <t>Работа в команде (пр), К426// Философия (пр), К427</t>
@@ -439,7 +544,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -458,12 +563,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="57">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -580,6 +691,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -709,6 +833,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -854,6 +991,19 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1072,6 +1222,17 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1189,7 +1350,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="225">
+  <cellXfs count="254">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1228,28 +1389,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,6 +1422,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="255"/>
     </xf>
@@ -1270,15 +1435,17 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1288,39 +1455,43 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1331,80 +1502,208 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="52" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1413,127 +1712,70 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1545,187 +1787,145 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2056,7 +2256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2065,10 +2265,11 @@
     <col min="4" max="4" width="21" style="2" customWidth="1"/>
     <col min="5" max="5" width="21.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="23.28515625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2076,15 +2277,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2092,41 +2293,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="44"/>
+      <c r="C6" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="49"/>
       <c r="E6" s="10">
         <v>1</v>
       </c>
@@ -2134,35 +2335,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="70"/>
+      <c r="D7" s="151"/>
       <c r="E7" s="14" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="83" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="159" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="159"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>0</v>
@@ -2173,382 +2374,459 @@
       <c r="D9" s="19"/>
       <c r="E9" s="20"/>
       <c r="F9" s="21"/>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="23">
+      <c r="G9" s="22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="71" t="s">
+      <c r="C10" s="152" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="154"/>
+      <c r="G10" s="78" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26">
+        <v>2</v>
+      </c>
+      <c r="C11" s="112" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="113"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="74" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
+        <v>3</v>
+      </c>
+      <c r="C12" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="114"/>
+      <c r="G12" s="77" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
+        <v>4</v>
+      </c>
+      <c r="C13" s="156"/>
+      <c r="D13" s="157"/>
+      <c r="E13" s="157"/>
+      <c r="F13" s="158"/>
+      <c r="G13" s="83"/>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29">
+        <v>5</v>
+      </c>
+      <c r="C14" s="105" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="155"/>
+      <c r="E14" s="155"/>
+      <c r="F14" s="108"/>
+      <c r="G14" s="79" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="31">
+        <v>1</v>
+      </c>
+      <c r="C15" s="109" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="77" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
+        <v>2</v>
+      </c>
+      <c r="C16" s="145" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="147"/>
+      <c r="G16" s="81" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
+        <v>3</v>
+      </c>
+      <c r="C17" s="96"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="72"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26">
+        <v>4</v>
+      </c>
+      <c r="C18" s="99"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="101"/>
+      <c r="G18" s="77"/>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="32"/>
+      <c r="B19" s="33">
+        <v>5</v>
+      </c>
+      <c r="C19" s="102" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="81" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="31">
+        <v>1</v>
+      </c>
+      <c r="C20" s="118" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="84" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
+        <v>2</v>
+      </c>
+      <c r="C21" s="166" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="167"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="168"/>
+      <c r="G21" s="77" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="25"/>
+      <c r="B22" s="26">
+        <v>3</v>
+      </c>
+      <c r="C22" s="163" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="164"/>
+      <c r="E22" s="164"/>
+      <c r="F22" s="165"/>
+      <c r="G22" s="77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="25"/>
+      <c r="B23" s="26">
+        <v>4</v>
+      </c>
+      <c r="C23" s="169"/>
+      <c r="D23" s="170"/>
+      <c r="E23" s="170"/>
+      <c r="F23" s="171"/>
+      <c r="G23" s="73"/>
+    </row>
+    <row r="24" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="35"/>
+      <c r="B24" s="29">
+        <v>5</v>
+      </c>
+      <c r="C24" s="93" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="79" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="31">
+        <v>1</v>
+      </c>
+      <c r="C25" s="160" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" s="161"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="25"/>
+      <c r="B26" s="24">
+        <v>2</v>
+      </c>
+      <c r="C26" s="112" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="113"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="114"/>
+      <c r="G26" s="82" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="25"/>
+      <c r="B27" s="26">
+        <v>3</v>
+      </c>
+      <c r="C27" s="148"/>
+      <c r="D27" s="149"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="150"/>
+      <c r="G27" s="27"/>
+    </row>
+    <row r="28" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="25"/>
+      <c r="B28" s="26">
+        <v>4</v>
+      </c>
+      <c r="C28" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="113"/>
+      <c r="E28" s="113"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="77" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="35"/>
+      <c r="B29" s="29">
+        <v>5</v>
+      </c>
+      <c r="C29" s="115"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="71"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="31">
+        <v>1</v>
+      </c>
+      <c r="C30" s="109"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="84"/>
+    </row>
+    <row r="31" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="37"/>
+      <c r="B31" s="26">
+        <v>2</v>
+      </c>
+      <c r="C31" s="105" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="106"/>
+      <c r="E31" s="107" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="73"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25">
-        <v>2</v>
-      </c>
-      <c r="C11" s="74" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="76"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="F31" s="108"/>
+      <c r="G31" s="77" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="37"/>
+      <c r="B32" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="74" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="76"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C32" s="124"/>
+      <c r="D32" s="125"/>
+      <c r="E32" s="125"/>
+      <c r="F32" s="126"/>
+      <c r="G32" s="72"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="80"/>
+      <c r="B33" s="33">
         <v>4</v>
       </c>
-      <c r="C13" s="80"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="82"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="C33" s="142"/>
+      <c r="D33" s="143"/>
+      <c r="E33" s="143"/>
+      <c r="F33" s="144"/>
+      <c r="G33" s="81"/>
+    </row>
+    <row r="34" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="38"/>
+      <c r="B34" s="29">
         <v>5</v>
       </c>
-      <c r="C14" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="79"/>
-    </row>
-    <row r="15" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="29">
-        <v>1</v>
-      </c>
-      <c r="C15" s="96" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="97"/>
-      <c r="E15" s="97"/>
-      <c r="F15" s="98"/>
-    </row>
-    <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
-        <v>2</v>
-      </c>
-      <c r="C16" s="64" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="66"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="C34" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="79" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="31">
         <v>3</v>
       </c>
-      <c r="C17" s="129"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="131"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25">
+      <c r="C35" s="127" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="129"/>
+      <c r="G35" s="84" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="40"/>
+      <c r="B36" s="26">
         <v>4</v>
       </c>
-      <c r="C18" s="132"/>
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="134"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="30"/>
-      <c r="B19" s="31">
+      <c r="C36" s="133"/>
+      <c r="D36" s="134"/>
+      <c r="E36" s="134"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="77"/>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="41"/>
+      <c r="B37" s="29">
         <v>5</v>
       </c>
-      <c r="C19" s="135" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="137"/>
-    </row>
-    <row r="20" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="29">
-        <v>1</v>
-      </c>
-      <c r="C20" s="90" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" s="91"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="92"/>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
-        <v>2</v>
-      </c>
-      <c r="C21" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="94"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="95"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25">
-        <v>3</v>
-      </c>
-      <c r="C22" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="88"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="89"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25">
-        <v>4</v>
-      </c>
-      <c r="C23" s="99"/>
-      <c r="D23" s="100"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="101"/>
-    </row>
-    <row r="24" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="32"/>
-      <c r="B24" s="27">
-        <v>5</v>
-      </c>
-      <c r="C24" s="123" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="125"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="29">
-        <v>1</v>
-      </c>
-      <c r="C25" s="84" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="86"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="24"/>
-      <c r="B26" s="23">
-        <v>2</v>
-      </c>
-      <c r="C26" s="74" t="s">
+      <c r="C37" s="139" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="141"/>
+      <c r="G37" s="75" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="75"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="76"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25">
-        <v>3</v>
-      </c>
-      <c r="C27" s="67"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69"/>
-    </row>
-    <row r="28" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="24"/>
-      <c r="B28" s="25">
-        <v>4</v>
-      </c>
-      <c r="C28" s="74" t="s">
+    </row>
+    <row r="38" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="42"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="136"/>
+      <c r="D38" s="137"/>
+      <c r="E38" s="137"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="44"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="45"/>
+      <c r="B39" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="118" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="119"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="85" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="46"/>
+      <c r="B40" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="130" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="75"/>
-      <c r="E28" s="75"/>
-      <c r="F28" s="76"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="32"/>
-      <c r="B29" s="27">
-        <v>5</v>
-      </c>
-      <c r="C29" s="140"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="141"/>
-      <c r="F29" s="142"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="29">
-        <v>1</v>
-      </c>
-      <c r="C30" s="96"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="97"/>
-      <c r="F30" s="98"/>
-    </row>
-    <row r="31" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="33"/>
-      <c r="B31" s="25">
-        <v>2</v>
-      </c>
-      <c r="C31" s="77" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="138"/>
-      <c r="E31" s="139" t="s">
-        <v>59</v>
-      </c>
-      <c r="F31" s="79"/>
-    </row>
-    <row r="32" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="33"/>
-      <c r="B32" s="25">
-        <v>3</v>
-      </c>
-      <c r="C32" s="105"/>
-      <c r="D32" s="106"/>
-      <c r="E32" s="106"/>
-      <c r="F32" s="107"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="63"/>
-      <c r="B33" s="31">
-        <v>4</v>
-      </c>
-      <c r="C33" s="126"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="128"/>
-    </row>
-    <row r="34" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="34"/>
-      <c r="B34" s="27">
-        <v>5</v>
-      </c>
-      <c r="C34" s="123" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="124"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="125"/>
-    </row>
-    <row r="35" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="29">
-        <v>3</v>
-      </c>
-      <c r="C35" s="108" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="109"/>
-      <c r="E35" s="109"/>
-      <c r="F35" s="110"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="36"/>
-      <c r="B36" s="25">
-        <v>4</v>
-      </c>
-      <c r="C36" s="114"/>
-      <c r="D36" s="115"/>
-      <c r="E36" s="115"/>
-      <c r="F36" s="116"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="37"/>
-      <c r="B37" s="27">
-        <v>5</v>
-      </c>
-      <c r="C37" s="120" t="s">
-        <v>102</v>
-      </c>
-      <c r="D37" s="121"/>
-      <c r="E37" s="121"/>
-      <c r="F37" s="122"/>
-    </row>
-    <row r="38" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="38"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="117"/>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118"/>
-      <c r="F38" s="119"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A39" s="40"/>
-      <c r="B39" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="90" t="s">
-        <v>54</v>
-      </c>
-      <c r="D39" s="91"/>
-      <c r="E39" s="91"/>
-      <c r="F39" s="92"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A40" s="41"/>
-      <c r="B40" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="111" t="s">
+      <c r="D40" s="131"/>
+      <c r="E40" s="131"/>
+      <c r="F40" s="132"/>
+      <c r="G40" s="76" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="48"/>
+      <c r="B41" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="112"/>
-      <c r="E40" s="112"/>
-      <c r="F40" s="113"/>
-    </row>
-    <row r="41" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="43"/>
-      <c r="B41" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="102" t="s">
-        <v>52</v>
-      </c>
-      <c r="D41" s="103"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="104"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C41" s="121" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="122"/>
+      <c r="E41" s="122"/>
+      <c r="F41" s="123"/>
+      <c r="G41" s="75" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B43" s="2" t="s">
         <v>15</v>
       </c>
@@ -2556,7 +2834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
@@ -2566,25 +2844,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C33:F33"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C7:D7"/>
@@ -2601,6 +2860,25 @@
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2631,7 +2909,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2640,10 +2918,11 @@
     <col min="4" max="4" width="17.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="19" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2651,15 +2930,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2667,41 +2946,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="44"/>
+      <c r="C6" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="49"/>
       <c r="E6" s="10">
         <v>2</v>
       </c>
@@ -2709,363 +2988,427 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="70"/>
+      <c r="D7" s="151"/>
       <c r="E7" s="14" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="83" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="159" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="159"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="48"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="23">
+      <c r="D9" s="51"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="93" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="95"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25">
+      <c r="C10" s="166" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="168"/>
+      <c r="G10" s="82" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="77" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="79"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="105" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="82" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="146" t="s">
+      <c r="C12" s="197" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="198"/>
+      <c r="E12" s="198"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="77" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29">
+        <v>4</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="201"/>
+      <c r="E13" s="201"/>
+      <c r="F13" s="202"/>
+      <c r="G13" s="36"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="31">
+        <v>1</v>
+      </c>
+      <c r="C14" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
+      <c r="F14" s="196"/>
+      <c r="G14" s="78" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26">
+        <v>2</v>
+      </c>
+      <c r="C15" s="203"/>
+      <c r="D15" s="204"/>
+      <c r="E15" s="204"/>
+      <c r="F15" s="205"/>
+      <c r="G15" s="86"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
+        <v>3</v>
+      </c>
+      <c r="C16" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="77" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="35"/>
+      <c r="B17" s="29">
+        <v>4</v>
+      </c>
+      <c r="C17" s="191"/>
+      <c r="D17" s="192"/>
+      <c r="E17" s="192"/>
+      <c r="F17" s="193"/>
+      <c r="G17" s="71"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="31">
+        <v>1</v>
+      </c>
+      <c r="C18" s="152" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="154"/>
+      <c r="G18" s="77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="25"/>
+      <c r="B19" s="26">
+        <v>2</v>
+      </c>
+      <c r="C19" s="166" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="167"/>
+      <c r="E19" s="167"/>
+      <c r="F19" s="168"/>
+      <c r="G19" s="77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
+        <v>3</v>
+      </c>
+      <c r="C20" s="124"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="77"/>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="35"/>
+      <c r="B21" s="29">
+        <v>4</v>
+      </c>
+      <c r="C21" s="181"/>
+      <c r="D21" s="182"/>
+      <c r="E21" s="182"/>
+      <c r="F21" s="183"/>
+      <c r="G21" s="79"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="31">
+        <v>2</v>
+      </c>
+      <c r="C22" s="127" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="147"/>
-      <c r="E12" s="147"/>
-      <c r="F12" s="148"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="84" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="25"/>
+      <c r="B23" s="26">
+        <v>3</v>
+      </c>
+      <c r="C23" s="163" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="164"/>
+      <c r="E23" s="164"/>
+      <c r="F23" s="165"/>
+      <c r="G23" s="82" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
         <v>4</v>
       </c>
-      <c r="C13" s="149"/>
-      <c r="D13" s="150"/>
-      <c r="E13" s="150"/>
-      <c r="F13" s="151"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="29">
+      <c r="C24" s="124"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="27"/>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="32"/>
+      <c r="B25" s="33">
+        <v>5</v>
+      </c>
+      <c r="C25" s="178" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="179"/>
+      <c r="E25" s="179"/>
+      <c r="F25" s="180"/>
+      <c r="G25" s="81" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="54">
         <v>1</v>
       </c>
-      <c r="C14" s="143" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="145"/>
-    </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25">
+      <c r="C26" s="187" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" s="188"/>
+      <c r="E26" s="189" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="190"/>
+      <c r="G26" s="91" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="37"/>
+      <c r="B27" s="55">
         <v>2</v>
       </c>
-      <c r="C15" s="152"/>
-      <c r="D15" s="153"/>
-      <c r="E15" s="153"/>
-      <c r="F15" s="154"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="C27" s="124"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="82"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="37"/>
+      <c r="B28" s="55">
+        <v>4</v>
+      </c>
+      <c r="C28" s="163" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="164"/>
+      <c r="E28" s="164"/>
+      <c r="F28" s="165"/>
+      <c r="G28" s="82" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="38"/>
+      <c r="B29" s="56">
+        <v>5</v>
+      </c>
+      <c r="C29" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="185"/>
+      <c r="E29" s="185"/>
+      <c r="F29" s="186"/>
+      <c r="G29" s="75" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="31">
+        <v>1</v>
+      </c>
+      <c r="C30" s="127" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="128"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="129"/>
+      <c r="G30" s="85" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="40"/>
+      <c r="B31" s="26">
+        <v>2</v>
+      </c>
+      <c r="C31" s="124"/>
+      <c r="D31" s="125"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="72"/>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="41"/>
+      <c r="B32" s="29">
         <v>3</v>
       </c>
-      <c r="C16" s="132" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="134"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="32"/>
-      <c r="B17" s="27">
-        <v>4</v>
-      </c>
-      <c r="C17" s="155"/>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156"/>
-      <c r="F17" s="157"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="29">
-        <v>1</v>
-      </c>
-      <c r="C18" s="71" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="73"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25">
-        <v>2</v>
-      </c>
-      <c r="C19" s="93" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="94"/>
-      <c r="E19" s="94"/>
-      <c r="F19" s="95"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
-        <v>3</v>
-      </c>
-      <c r="C20" s="105"/>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="107"/>
-    </row>
-    <row r="21" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="32"/>
-      <c r="B21" s="27">
-        <v>4</v>
-      </c>
-      <c r="C21" s="158"/>
-      <c r="D21" s="159"/>
-      <c r="E21" s="159"/>
-      <c r="F21" s="160"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="29">
-        <v>2</v>
-      </c>
-      <c r="C22" s="108" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="110"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25">
-        <v>3</v>
-      </c>
-      <c r="C23" s="87" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="89"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
-        <v>4</v>
-      </c>
-      <c r="C24" s="105"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="107"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="30"/>
-      <c r="B25" s="31">
-        <v>5</v>
-      </c>
-      <c r="C25" s="167" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="168"/>
-      <c r="E25" s="168"/>
-      <c r="F25" s="169"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="49">
-        <v>1</v>
-      </c>
-      <c r="C26" s="173" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="174"/>
-      <c r="E26" s="175" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="176"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="50">
-        <v>2</v>
-      </c>
-      <c r="C27" s="105"/>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="107"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="33"/>
-      <c r="B28" s="50">
-        <v>4</v>
-      </c>
-      <c r="C28" s="87" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="89"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="34"/>
-      <c r="B29" s="51">
-        <v>5</v>
-      </c>
-      <c r="C29" s="170" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="171"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="172"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="29">
-        <v>1</v>
-      </c>
-      <c r="C30" s="108" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="109"/>
-      <c r="E30" s="109"/>
-      <c r="F30" s="110"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="36"/>
-      <c r="B31" s="25">
-        <v>2</v>
-      </c>
-      <c r="C31" s="105"/>
-      <c r="D31" s="106"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="107"/>
-    </row>
-    <row r="32" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="37"/>
-      <c r="B32" s="27">
-        <v>3</v>
-      </c>
-      <c r="C32" s="158"/>
-      <c r="D32" s="159"/>
-      <c r="E32" s="159"/>
-      <c r="F32" s="160"/>
-    </row>
-    <row r="33" spans="1:6" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="38"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="161"/>
-      <c r="D33" s="162"/>
-      <c r="E33" s="162"/>
-      <c r="F33" s="163"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="59"/>
-      <c r="B34" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="96" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="97"/>
-      <c r="E34" s="97"/>
-      <c r="F34" s="98"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="60"/>
-      <c r="B35" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="94"/>
-      <c r="E35" s="94"/>
-      <c r="F35" s="95"/>
-    </row>
-    <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="61"/>
-      <c r="B36" s="62" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="164" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="165"/>
-      <c r="E36" s="165"/>
-      <c r="F36" s="166"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C32" s="181"/>
+      <c r="D32" s="182"/>
+      <c r="E32" s="182"/>
+      <c r="F32" s="183"/>
+      <c r="G32" s="71"/>
+    </row>
+    <row r="33" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="42"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="172"/>
+      <c r="D33" s="173"/>
+      <c r="E33" s="173"/>
+      <c r="F33" s="174"/>
+      <c r="G33" s="57"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="67"/>
+      <c r="B34" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="109" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="110"/>
+      <c r="E34" s="110"/>
+      <c r="F34" s="111"/>
+      <c r="G34" s="85" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="68"/>
+      <c r="B35" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="166" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="167"/>
+      <c r="E35" s="167"/>
+      <c r="F35" s="168"/>
+      <c r="G35" s="82" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="69"/>
+      <c r="B36" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="175" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="176"/>
+      <c r="E36" s="176"/>
+      <c r="F36" s="177"/>
+      <c r="G36" s="75" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
         <v>15</v>
       </c>
@@ -3073,7 +3416,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -3083,6 +3426,23 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C22:F22"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C25:F25"/>
@@ -3096,23 +3456,6 @@
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C15:F15"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3143,7 +3486,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3152,10 +3495,11 @@
     <col min="4" max="4" width="18.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3163,15 +3507,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3179,41 +3523,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="44"/>
+      <c r="C6" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="49"/>
       <c r="E6" s="10">
         <v>3</v>
       </c>
@@ -3221,335 +3565,391 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="177" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="223" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="177"/>
+      <c r="D7" s="223"/>
       <c r="E7" s="14" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="83" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="159" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="159"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="48"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="23">
+      <c r="D9" s="51"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="181" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="182"/>
-      <c r="E10" s="182"/>
-      <c r="F10" s="183"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25">
+      <c r="C10" s="220" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="221"/>
+      <c r="E10" s="221"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="85"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="77"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="79"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="105"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="82"/>
+    </row>
+    <row r="12" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="126"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="128"/>
-    </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="C12" s="142"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="27"/>
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29">
         <v>4</v>
       </c>
-      <c r="C13" s="184"/>
-      <c r="D13" s="185"/>
-      <c r="E13" s="185"/>
-      <c r="F13" s="186"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="29">
+      <c r="C13" s="227"/>
+      <c r="D13" s="228"/>
+      <c r="E13" s="228"/>
+      <c r="F13" s="229"/>
+      <c r="G13" s="36"/>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="31">
         <v>1</v>
       </c>
-      <c r="C14" s="178"/>
-      <c r="D14" s="179"/>
-      <c r="E14" s="179"/>
-      <c r="F14" s="180"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25">
+      <c r="C14" s="224"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="226"/>
+      <c r="G14" s="34"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26">
         <v>2</v>
       </c>
-      <c r="C15" s="146"/>
-      <c r="D15" s="147"/>
-      <c r="E15" s="147"/>
-      <c r="F15" s="148"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="C15" s="197"/>
+      <c r="D15" s="198"/>
+      <c r="E15" s="198"/>
+      <c r="F15" s="199"/>
+      <c r="G15" s="82"/>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <v>3</v>
       </c>
-      <c r="C16" s="146" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="193"/>
-      <c r="E16" s="193"/>
-      <c r="F16" s="194"/>
-    </row>
-    <row r="17" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="32"/>
-      <c r="B17" s="27">
+      <c r="C16" s="197" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
+      <c r="F16" s="210"/>
+      <c r="G16" s="82" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="35"/>
+      <c r="B17" s="29">
         <v>4</v>
       </c>
-      <c r="C17" s="120" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="29">
+      <c r="C17" s="139" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="140"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="75" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="31">
         <v>2</v>
       </c>
-      <c r="C18" s="96" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="97"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="98"/>
-    </row>
-    <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25">
+      <c r="C18" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="25"/>
+      <c r="B19" s="26">
         <v>3</v>
       </c>
-      <c r="C19" s="146" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" s="193"/>
-      <c r="E19" s="193"/>
-      <c r="F19" s="194"/>
-    </row>
-    <row r="20" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
+      <c r="C19" s="197" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="209"/>
+      <c r="E19" s="209"/>
+      <c r="F19" s="210"/>
+      <c r="G19" s="82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
         <v>4</v>
       </c>
-      <c r="C20" s="146" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="193"/>
-      <c r="E20" s="193"/>
-      <c r="F20" s="194"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="32"/>
-      <c r="B21" s="27">
+      <c r="C20" s="197" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="209"/>
+      <c r="E20" s="209"/>
+      <c r="F20" s="210"/>
+      <c r="G20" s="82" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="35"/>
+      <c r="B21" s="29">
         <v>5</v>
       </c>
-      <c r="C21" s="190"/>
-      <c r="D21" s="191"/>
-      <c r="E21" s="191"/>
-      <c r="F21" s="192"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="C21" s="211"/>
+      <c r="D21" s="212"/>
+      <c r="E21" s="212"/>
+      <c r="F21" s="213"/>
+      <c r="G21" s="58"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="31">
         <v>1</v>
       </c>
-      <c r="C22" s="198" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="199"/>
-      <c r="E22" s="199"/>
-      <c r="F22" s="200"/>
-    </row>
-    <row r="23" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25">
+      <c r="C22" s="206" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="207"/>
+      <c r="E22" s="207"/>
+      <c r="F22" s="208"/>
+      <c r="G22" s="85" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="25"/>
+      <c r="B23" s="26">
         <v>2</v>
       </c>
-      <c r="C23" s="77" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="79"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
+      <c r="C23" s="105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="155"/>
+      <c r="E23" s="155"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="82" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
         <v>3</v>
       </c>
-      <c r="C24" s="93" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="95"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="32"/>
-      <c r="B25" s="27">
+      <c r="C24" s="166" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="167"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="168"/>
+      <c r="G24" s="82" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="35"/>
+      <c r="B25" s="29">
         <v>4</v>
       </c>
-      <c r="C25" s="190"/>
-      <c r="D25" s="191"/>
-      <c r="E25" s="191"/>
-      <c r="F25" s="192"/>
-    </row>
-    <row r="26" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="29">
+      <c r="C25" s="211"/>
+      <c r="D25" s="212"/>
+      <c r="E25" s="212"/>
+      <c r="F25" s="213"/>
+      <c r="G25" s="36"/>
+    </row>
+    <row r="26" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="31">
         <v>1</v>
       </c>
-      <c r="C26" s="96" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="98"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="25">
+      <c r="C26" s="109" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="85" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="37"/>
+      <c r="B27" s="26">
         <v>2</v>
       </c>
-      <c r="C27" s="146" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="193"/>
-      <c r="E27" s="193"/>
-      <c r="F27" s="194"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="63"/>
-      <c r="B28" s="31">
+      <c r="C27" s="197" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="209"/>
+      <c r="E27" s="209"/>
+      <c r="F27" s="210"/>
+      <c r="G27" s="82" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="80"/>
+      <c r="B28" s="33">
         <v>3</v>
       </c>
-      <c r="C28" s="93" t="s">
+      <c r="C28" s="166" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="167"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="168"/>
+      <c r="G28" s="82" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="38"/>
+      <c r="B29" s="29">
+        <v>4</v>
+      </c>
+      <c r="C29" s="217" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="218"/>
+      <c r="E29" s="218"/>
+      <c r="F29" s="219"/>
+      <c r="G29" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="94"/>
-      <c r="E28" s="94"/>
-      <c r="F28" s="95"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="34"/>
-      <c r="B29" s="27">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="24">
+        <v>1</v>
+      </c>
+      <c r="C30" s="220"/>
+      <c r="D30" s="221"/>
+      <c r="E30" s="221"/>
+      <c r="F30" s="222"/>
+      <c r="G30" s="59"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="40"/>
+      <c r="B31" s="26">
+        <v>2</v>
+      </c>
+      <c r="C31" s="166" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="167"/>
+      <c r="E31" s="167"/>
+      <c r="F31" s="168"/>
+      <c r="G31" s="82" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="26">
+        <v>3</v>
+      </c>
+      <c r="C32" s="105" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="155"/>
+      <c r="E32" s="155"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="82" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="48"/>
+      <c r="B33" s="61">
         <v>4</v>
       </c>
-      <c r="C29" s="195" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="196"/>
-      <c r="E29" s="196"/>
-      <c r="F29" s="197"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="23">
-        <v>1</v>
-      </c>
-      <c r="C30" s="181"/>
-      <c r="D30" s="182"/>
-      <c r="E30" s="182"/>
-      <c r="F30" s="183"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="36"/>
-      <c r="B31" s="25">
-        <v>2</v>
-      </c>
-      <c r="C31" s="93" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="94"/>
-      <c r="E31" s="94"/>
-      <c r="F31" s="95"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="36"/>
-      <c r="B32" s="25">
-        <v>3</v>
-      </c>
-      <c r="C32" s="77" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="79"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="43"/>
-      <c r="B33" s="53">
-        <v>4</v>
-      </c>
-      <c r="C33" s="187"/>
-      <c r="D33" s="188"/>
-      <c r="E33" s="188"/>
-      <c r="F33" s="189"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="214"/>
+      <c r="D33" s="215"/>
+      <c r="E33" s="215"/>
+      <c r="F33" s="216"/>
+      <c r="G33" s="36"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B35" s="2" t="s">
         <v>15</v>
       </c>
@@ -3557,7 +3957,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
@@ -3567,6 +3967,20 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C28:F28"/>
@@ -3579,20 +3993,6 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C8:F8"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3623,7 +4023,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3632,10 +4032,11 @@
     <col min="4" max="4" width="19" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3643,15 +4044,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3659,41 +4060,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="44"/>
+      <c r="C6" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="49"/>
       <c r="E6" s="10">
         <v>4</v>
       </c>
@@ -3701,326 +4102,380 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="68.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="68.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="70"/>
+      <c r="D7" s="151"/>
       <c r="E7" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="55"/>
-      <c r="E8" s="54"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="63"/>
+      <c r="E8" s="62"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="55"/>
-      <c r="E9" s="54"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="63"/>
+      <c r="E9" s="62"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="48"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="23">
+      <c r="D10" s="51"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="24">
         <v>1</v>
       </c>
-      <c r="C11" s="204" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="205"/>
-      <c r="E11" s="205"/>
-      <c r="F11" s="206"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="248" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="250"/>
+      <c r="G11" s="87" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>2</v>
       </c>
-      <c r="C12" s="207" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="208"/>
-      <c r="E12" s="208"/>
-      <c r="F12" s="209"/>
-    </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="239" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="240"/>
+      <c r="E12" s="240"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="89" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>3</v>
       </c>
-      <c r="C13" s="93"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="95"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="C13" s="166"/>
+      <c r="D13" s="167"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="168"/>
+      <c r="G13" s="82"/>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29">
         <v>4</v>
       </c>
-      <c r="C14" s="210"/>
-      <c r="D14" s="211"/>
-      <c r="E14" s="211"/>
-      <c r="F14" s="212"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="29">
+      <c r="C14" s="251"/>
+      <c r="D14" s="252"/>
+      <c r="E14" s="252"/>
+      <c r="F14" s="253"/>
+      <c r="G14" s="75"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="31">
         <v>1</v>
       </c>
-      <c r="C15" s="201"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="202"/>
-      <c r="F15" s="203"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="C15" s="245"/>
+      <c r="D15" s="246"/>
+      <c r="E15" s="246"/>
+      <c r="F15" s="247"/>
+      <c r="G15" s="84"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <v>2</v>
       </c>
-      <c r="C16" s="93" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="95"/>
-    </row>
-    <row r="17" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="C16" s="166" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="167"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="89" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <v>3</v>
       </c>
-      <c r="C17" s="126"/>
-      <c r="D17" s="127"/>
-      <c r="E17" s="127"/>
-      <c r="F17" s="128"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="32"/>
-      <c r="B18" s="27">
+      <c r="C17" s="142"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="77"/>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35"/>
+      <c r="B18" s="29">
         <v>4</v>
       </c>
-      <c r="C18" s="164" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="165"/>
-      <c r="E18" s="165"/>
-      <c r="F18" s="166"/>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="29">
+      <c r="C18" s="175" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="176"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="177"/>
+      <c r="G18" s="88" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="31">
         <v>2</v>
       </c>
-      <c r="C19" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="109"/>
-      <c r="E19" s="109"/>
-      <c r="F19" s="110"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
+      <c r="C19" s="127" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="128"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="85" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
         <v>3</v>
       </c>
-      <c r="C20" s="93" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="94"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="95"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
+      <c r="C20" s="166" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="167"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="168"/>
+      <c r="G20" s="82" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
         <v>4</v>
       </c>
-      <c r="C21" s="93" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="94"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="95"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="32"/>
-      <c r="B22" s="27">
+      <c r="C21" s="166" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="167"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="168"/>
+      <c r="G21" s="82" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="35"/>
+      <c r="B22" s="29">
         <v>5</v>
       </c>
-      <c r="C22" s="219" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="220"/>
-      <c r="E22" s="220"/>
-      <c r="F22" s="221"/>
-    </row>
-    <row r="23" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="29">
+      <c r="C22" s="233" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="234"/>
+      <c r="E22" s="234"/>
+      <c r="F22" s="235"/>
+      <c r="G22" s="75" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="31">
         <v>1</v>
       </c>
-      <c r="C23" s="222" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="223"/>
-      <c r="E23" s="223"/>
-      <c r="F23" s="224"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
+      <c r="C23" s="236" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="237"/>
+      <c r="E23" s="237"/>
+      <c r="F23" s="238"/>
+      <c r="G23" s="92" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
         <v>2</v>
       </c>
-      <c r="C24" s="207" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="208"/>
-      <c r="E24" s="208"/>
-      <c r="F24" s="209"/>
-    </row>
-    <row r="25" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
+      <c r="C24" s="239" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="240"/>
+      <c r="E24" s="240"/>
+      <c r="F24" s="241"/>
+      <c r="G24" s="77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
         <v>3</v>
       </c>
-      <c r="C25" s="87" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="89"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="32"/>
-      <c r="B26" s="27">
+      <c r="C25" s="163" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="164"/>
+      <c r="E25" s="164"/>
+      <c r="F25" s="165"/>
+      <c r="G25" s="77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="35"/>
+      <c r="B26" s="29">
         <v>4</v>
       </c>
-      <c r="C26" s="216"/>
-      <c r="D26" s="217"/>
-      <c r="E26" s="217"/>
-      <c r="F26" s="218"/>
-    </row>
-    <row r="27" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="29">
+      <c r="C26" s="230"/>
+      <c r="D26" s="231"/>
+      <c r="E26" s="231"/>
+      <c r="F26" s="232"/>
+      <c r="G26" s="72"/>
+    </row>
+    <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="31">
         <v>1</v>
       </c>
-      <c r="C27" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" s="109"/>
-      <c r="E27" s="109"/>
-      <c r="F27" s="110"/>
-    </row>
-    <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="33"/>
-      <c r="B28" s="25">
+      <c r="C27" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="128"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="129"/>
+      <c r="G27" s="85" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="37"/>
+      <c r="B28" s="26">
         <v>2</v>
       </c>
-      <c r="C28" s="213" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" s="214"/>
-      <c r="E28" s="214"/>
-      <c r="F28" s="215"/>
-    </row>
-    <row r="29" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="33"/>
-      <c r="B29" s="25">
+      <c r="C28" s="242" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="243"/>
+      <c r="E28" s="243"/>
+      <c r="F28" s="244"/>
+      <c r="G28" s="82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="37"/>
+      <c r="B29" s="26">
         <v>3</v>
       </c>
-      <c r="C29" s="93" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="94"/>
-      <c r="E29" s="94"/>
-      <c r="F29" s="95"/>
-    </row>
-    <row r="30" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="34"/>
-      <c r="B30" s="27">
+      <c r="C29" s="166" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="167"/>
+      <c r="E29" s="167"/>
+      <c r="F29" s="168"/>
+      <c r="G29" s="82" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="38"/>
+      <c r="B30" s="29">
         <v>4</v>
       </c>
-      <c r="C30" s="149"/>
-      <c r="D30" s="150"/>
-      <c r="E30" s="150"/>
-      <c r="F30" s="151"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="23">
+      <c r="C30" s="200"/>
+      <c r="D30" s="201"/>
+      <c r="E30" s="201"/>
+      <c r="F30" s="202"/>
+      <c r="G30" s="27"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="24">
         <v>1</v>
       </c>
-      <c r="C31" s="181" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="182"/>
-      <c r="E31" s="182"/>
-      <c r="F31" s="183"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="36"/>
-      <c r="B32" s="25">
+      <c r="C31" s="220" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="221"/>
+      <c r="E31" s="221"/>
+      <c r="F31" s="222"/>
+      <c r="G31" s="34"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="26">
         <v>2</v>
       </c>
-      <c r="C32" s="126"/>
-      <c r="D32" s="127"/>
-      <c r="E32" s="127"/>
-      <c r="F32" s="128"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="43"/>
-      <c r="B33" s="53"/>
-      <c r="C33" s="187"/>
-      <c r="D33" s="188"/>
-      <c r="E33" s="188"/>
-      <c r="F33" s="189"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C32" s="142"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="144"/>
+      <c r="G32" s="27"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="48"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="214"/>
+      <c r="D33" s="215"/>
+      <c r="E33" s="215"/>
+      <c r="F33" s="216"/>
+      <c r="G33" s="71"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B34" s="2" t="s">
         <v>15</v>
       </c>
@@ -4028,7 +4483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
@@ -4038,11 +4493,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
@@ -4050,18 +4512,11 @@
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
